--- a/data/trans_dic/IP1007-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos convulsivos</t>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,11</t>
+          <t>0,1; 1,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,24</t>
+          <t>0,15; 1,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,08; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,98</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,7</t>
+          <t>0,16; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,4</t>
+          <t>0,04; 0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,55</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2854</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3481</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2313</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3514</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2722</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5883</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4971</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3560</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>523; 5660</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5189</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6624</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3955</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3718</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4314</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3619</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3628</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3196</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>597; 5276</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3483</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3181</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>524; 4717</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6255</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1256; 6994</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4299</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>628; 5923</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2275; 9594</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>569; 5723</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1157; 7500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1007-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Edad-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,12</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,32</t>
+          <t>0,15; 1,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,42 +1118,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,08; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,97</t>
+          <t>0,17; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,68</t>
+          <t>0,17; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,39</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2854</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3481</t>
+          <t>0; 3462</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2313</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 4185</t>
         </is>
       </c>
     </row>
@@ -1580,22 +1580,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2722</t>
+          <t>0; 2648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5883</t>
+          <t>0; 7912</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 4996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3560</t>
+          <t>0; 3250</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>523; 5660</t>
+          <t>522; 5480</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5189</t>
+          <t>0; 4053</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6624</t>
+          <t>0; 7051</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>0; 4388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3718</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4314</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3619</t>
+          <t>0; 3188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 3611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3196</t>
+          <t>0; 3200</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597; 5276</t>
+          <t>597; 5007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 3213</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>524; 4717</t>
+          <t>523; 5144</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5008</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6255</t>
+          <t>0; 5816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1256; 6994</t>
+          <t>1256; 7304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 3715</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>628; 5923</t>
+          <t>624; 5837</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2275; 9594</t>
+          <t>2362; 9587</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>569; 5723</t>
+          <t>567; 5833</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1157; 7500</t>
+          <t>1158; 7525</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1007-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,77</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 1,11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,89</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,26</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 1,08</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,81</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -845,22 +845,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,25</t>
+          <t>0,01; 1,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,37 +1118,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,76</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,71</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,83</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 1,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,78</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,68</t>
+          <t>0,14; 0,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,05; 0,55</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3426</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3462</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 2848</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4019</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>0; 4950</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7912</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 2279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5397</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3250</t>
+          <t>0; 5836</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>522; 5480</t>
+          <t>522; 5613</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4053</t>
+          <t>0; 4481</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 7051</t>
+          <t>0; 5891</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 4704</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1214</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4745</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3796</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597; 5007</t>
+          <t>22; 4974</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3213</t>
+          <t>0; 2990</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>523; 5144</t>
+          <t>1259; 7086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5484</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5816</t>
+          <t>622; 5324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1256; 7304</t>
+          <t>524; 5498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3715</t>
+          <t>0; 5622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>624; 5837</t>
+          <t>0; 5820</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2362; 9587</t>
+          <t>1931; 9895</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>567; 5833</t>
+          <t>567; 5762</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1158; 7525</t>
+          <t>696; 7921</t>
         </is>
       </c>
     </row>
